--- a/BM03 Đăng ký hoặc hủy môi trường và công cụ làm việc cho đối tác.xlsx
+++ b/BM03 Đăng ký hoặc hủy môi trường và công cụ làm việc cho đối tác.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmcglobalcompany-my.sharepoint.com/personal/nnthinh_cmcglobal_vn/Documents/Desktop/daily/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cmcglobalcompany-my.sharepoint.com/personal/nnthinh_cmcglobal_vn/Documents/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{44C9E846-A4EC-463B-A899-5A3DAD3EFB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D969FBE1-832A-4CA0-AFFB-D5DC38959C9A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3A44ADB-EC7E-4F6C-AE67-E476C2B7E942}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-90" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -120,28 +120,28 @@
     <t>Giám đốc đơn vị</t>
   </si>
   <si>
-    <t>Nguyễn Văn Thành</t>
-  </si>
-  <si>
-    <t>J2CPQ629MT</t>
-  </si>
-  <si>
     <t>D0:11:E5:6B:90:EB</t>
   </si>
   <si>
-    <t>Mac mini và 2 màn hình</t>
-  </si>
-  <si>
-    <t>Nguyễn Tiến Dũng</t>
-  </si>
-  <si>
-    <t>97PJJM3</t>
-  </si>
-  <si>
     <t>74:86:E2:0C:6B:F8</t>
   </si>
   <si>
-    <t>PC DELL và 2 màn hình</t>
+    <t>Nguyễn Đức Hiến</t>
+  </si>
+  <si>
+    <t>D94GVWKPN</t>
+  </si>
+  <si>
+    <t>Phạm Ngọc Diệp</t>
+  </si>
+  <si>
+    <t>5CG1163B9K</t>
+  </si>
+  <si>
+    <t>Laptop Dell</t>
+  </si>
+  <si>
+    <t>Laptop HP</t>
   </si>
 </sst>
 </file>
@@ -290,21 +290,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right/>
       <top style="thin">
         <color indexed="64"/>
@@ -323,6 +308,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -400,12 +398,6 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -415,66 +407,70 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -792,287 +788,287 @@
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
-      <c r="B3" s="46"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="47"/>
-      <c r="I3" s="47"/>
-      <c r="J3" s="47"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="47"/>
-      <c r="M3" s="47"/>
-      <c r="N3" s="47"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="47"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="47"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="47"/>
-      <c r="U3" s="47"/>
-      <c r="V3" s="42"/>
-      <c r="W3" s="42"/>
-      <c r="X3" s="42"/>
-      <c r="Y3" s="42"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
+      <c r="P3" s="39"/>
+      <c r="Q3" s="39"/>
+      <c r="R3" s="39"/>
+      <c r="S3" s="39"/>
+      <c r="T3" s="39"/>
+      <c r="U3" s="39"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
+      <c r="X3" s="34"/>
+      <c r="Y3" s="34"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="44"/>
-      <c r="D4" s="44"/>
-      <c r="E4" s="44"/>
-      <c r="F4" s="44"/>
-      <c r="G4" s="44"/>
-      <c r="H4" s="44"/>
-      <c r="I4" s="44"/>
-      <c r="J4" s="44"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="42"/>
-      <c r="S4" s="42"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="42"/>
-      <c r="V4" s="42"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="42"/>
-      <c r="Y4" s="42"/>
+      <c r="A4" s="35"/>
+      <c r="B4" s="35"/>
+      <c r="C4" s="36"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="36"/>
+      <c r="G4" s="36"/>
+      <c r="H4" s="36"/>
+      <c r="I4" s="36"/>
+      <c r="J4" s="36"/>
+      <c r="K4" s="36"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="37"/>
+      <c r="Q4" s="37"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
+      <c r="X4" s="34"/>
+      <c r="Y4" s="34"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="44"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="44"/>
-      <c r="H5" s="44"/>
-      <c r="I5" s="44"/>
-      <c r="J5" s="44"/>
-      <c r="K5" s="44"/>
-      <c r="L5" s="44"/>
-      <c r="M5" s="44"/>
-      <c r="N5" s="44"/>
-      <c r="O5" s="44"/>
-      <c r="P5" s="44"/>
-      <c r="Q5" s="44"/>
-      <c r="R5" s="44"/>
-      <c r="S5" s="44"/>
-      <c r="T5" s="44"/>
-      <c r="U5" s="44"/>
-      <c r="V5" s="44"/>
-      <c r="W5" s="44"/>
-      <c r="X5" s="44"/>
-      <c r="Y5" s="44"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="36"/>
+      <c r="G5" s="36"/>
+      <c r="H5" s="36"/>
+      <c r="I5" s="36"/>
+      <c r="J5" s="36"/>
+      <c r="K5" s="36"/>
+      <c r="L5" s="36"/>
+      <c r="M5" s="36"/>
+      <c r="N5" s="36"/>
+      <c r="O5" s="36"/>
+      <c r="P5" s="36"/>
+      <c r="Q5" s="36"/>
+      <c r="R5" s="36"/>
+      <c r="S5" s="36"/>
+      <c r="T5" s="36"/>
+      <c r="U5" s="36"/>
+      <c r="V5" s="36"/>
+      <c r="W5" s="36"/>
+      <c r="X5" s="36"/>
+      <c r="Y5" s="36"/>
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
-      <c r="K6" s="49"/>
-      <c r="L6" s="49"/>
-      <c r="M6" s="49"/>
-      <c r="N6" s="49"/>
-      <c r="O6" s="49"/>
-      <c r="P6" s="49"/>
-      <c r="Q6" s="48"/>
-      <c r="R6" s="48"/>
-      <c r="S6" s="48"/>
-      <c r="T6" s="48"/>
-      <c r="U6" s="48"/>
-      <c r="V6" s="48"/>
-      <c r="W6" s="48"/>
-      <c r="X6" s="48"/>
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="29"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="29"/>
+      <c r="T6" s="29"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="29"/>
+      <c r="W6" s="29"/>
+      <c r="X6" s="29"/>
       <c r="Y6" s="3"/>
     </row>
     <row r="7" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="39" t="s">
+      <c r="C7" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D7" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="E7" s="30" t="s">
+      <c r="E7" s="32" t="s">
         <v>7</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="32" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="30" t="s">
+      <c r="H7" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="I7" s="30" t="s">
+      <c r="I7" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="K7" s="30" t="s">
+      <c r="K7" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30" t="s">
+      <c r="L7" s="32"/>
+      <c r="M7" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30" t="s">
+      <c r="N7" s="32"/>
+      <c r="O7" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="P7" s="30"/>
-      <c r="Q7" s="30" t="s">
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="40" t="s">
+      <c r="R7" s="32"/>
+      <c r="S7" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="T7" s="40"/>
-      <c r="U7" s="40" t="s">
+      <c r="T7" s="33"/>
+      <c r="U7" s="33" t="s">
         <v>18</v>
       </c>
-      <c r="V7" s="40"/>
-      <c r="W7" s="38"/>
+      <c r="V7" s="33"/>
+      <c r="W7" s="40"/>
     </row>
     <row r="8" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="30"/>
-      <c r="E8" s="30"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="32"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
       <c r="F8" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="G8" s="30"/>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
-      <c r="J8" s="30"/>
-      <c r="K8" s="30"/>
-      <c r="L8" s="30"/>
-      <c r="M8" s="30"/>
-      <c r="N8" s="30"/>
-      <c r="O8" s="30"/>
-      <c r="P8" s="30"/>
-      <c r="Q8" s="30"/>
-      <c r="R8" s="30"/>
-      <c r="S8" s="40"/>
-      <c r="T8" s="40"/>
-      <c r="U8" s="40" t="s">
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="V8" s="40"/>
-      <c r="W8" s="38"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="40"/>
     </row>
     <row r="9" spans="1:25" s="4" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="30"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="32"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="30"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="30"/>
-      <c r="K9" s="30"/>
-      <c r="L9" s="30"/>
-      <c r="M9" s="30"/>
-      <c r="N9" s="30"/>
-      <c r="O9" s="30"/>
-      <c r="P9" s="30"/>
-      <c r="Q9" s="30"/>
-      <c r="R9" s="30"/>
-      <c r="S9" s="40"/>
-      <c r="T9" s="40"/>
-      <c r="U9" s="41"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="38"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="33"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="42"/>
+      <c r="V9" s="42"/>
+      <c r="W9" s="40"/>
     </row>
     <row r="10" spans="1:25" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="30"/>
+      <c r="A10" s="32"/>
+      <c r="B10" s="32"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
       <c r="F10" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="30"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
-      <c r="J10" s="30"/>
-      <c r="K10" s="30"/>
-      <c r="L10" s="30"/>
-      <c r="M10" s="30"/>
-      <c r="N10" s="30"/>
-      <c r="O10" s="30"/>
-      <c r="P10" s="30"/>
-      <c r="Q10" s="30"/>
-      <c r="R10" s="30"/>
-      <c r="S10" s="40"/>
-      <c r="T10" s="40"/>
-      <c r="U10" s="41"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="38"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="33"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="42"/>
+      <c r="V10" s="42"/>
+      <c r="W10" s="40"/>
     </row>
     <row r="11" spans="1:25" s="4" customFormat="1" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="32"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="30"/>
-      <c r="L11" s="30"/>
-      <c r="M11" s="30"/>
-      <c r="N11" s="30"/>
-      <c r="O11" s="30"/>
-      <c r="P11" s="30"/>
-      <c r="Q11" s="30"/>
-      <c r="R11" s="30"/>
-      <c r="S11" s="40"/>
-      <c r="T11" s="40"/>
-      <c r="U11" s="41"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="38"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="42"/>
+      <c r="V11" s="42"/>
+      <c r="W11" s="40"/>
     </row>
     <row r="12" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="19">
         <v>4</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C12" s="21"/>
       <c r="D12" s="22" t="s">
@@ -1082,26 +1078,26 @@
       <c r="F12" s="24"/>
       <c r="G12" s="24"/>
       <c r="H12" s="24"/>
-      <c r="I12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="J12" s="25" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="36" t="s">
+      <c r="I12" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="L12" s="37"/>
-      <c r="M12" s="33"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="33"/>
-      <c r="P12" s="33"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="35"/>
+      <c r="J12" s="48" t="s">
+        <v>28</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>34</v>
+      </c>
+      <c r="L12" s="47"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="45"/>
+      <c r="O12" s="45"/>
+      <c r="P12" s="45"/>
+      <c r="Q12" s="45"/>
+      <c r="R12" s="45"/>
+      <c r="S12" s="43"/>
+      <c r="T12" s="43"/>
+      <c r="U12" s="44"/>
+      <c r="V12" s="44"/>
       <c r="W12" s="3"/>
     </row>
     <row r="13" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1119,28 +1115,28 @@
       <c r="F13" s="24"/>
       <c r="G13" s="24"/>
       <c r="H13" s="24"/>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="49" t="s">
         <v>33</v>
       </c>
-      <c r="J13" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="K13" s="36" t="s">
+      <c r="J13" s="48" t="s">
+        <v>29</v>
+      </c>
+      <c r="K13" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="L13" s="37"/>
-      <c r="M13" s="33"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="33"/>
-      <c r="P13" s="33"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="35"/>
-      <c r="W13" s="29"/>
-      <c r="X13" s="29"/>
+      <c r="L13" s="47"/>
+      <c r="M13" s="45"/>
+      <c r="N13" s="45"/>
+      <c r="O13" s="45"/>
+      <c r="P13" s="45"/>
+      <c r="Q13" s="45"/>
+      <c r="R13" s="45"/>
+      <c r="S13" s="43"/>
+      <c r="T13" s="43"/>
+      <c r="U13" s="44"/>
+      <c r="V13" s="44"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
       <c r="Y13" s="3"/>
     </row>
     <row r="14" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1154,20 +1150,20 @@
       <c r="H14" s="11"/>
       <c r="I14" s="17"/>
       <c r="J14" s="18"/>
-      <c r="K14" s="31"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="32"/>
-      <c r="V14" s="32"/>
-      <c r="W14" s="29"/>
-      <c r="X14" s="29"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="30"/>
+      <c r="W14" s="27"/>
+      <c r="X14" s="27"/>
       <c r="Y14" s="3"/>
     </row>
     <row r="15" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1181,20 +1177,20 @@
       <c r="H15" s="11"/>
       <c r="I15" s="17"/>
       <c r="J15" s="18"/>
-      <c r="K15" s="31"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="32"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="29"/>
-      <c r="X15" s="29"/>
+      <c r="K15" s="28"/>
+      <c r="L15" s="28"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
       <c r="Y15" s="3"/>
     </row>
     <row r="16" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1208,20 +1204,20 @@
       <c r="H16" s="11"/>
       <c r="I16" s="17"/>
       <c r="J16" s="18"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="27"/>
-      <c r="O16" s="27"/>
-      <c r="P16" s="27"/>
-      <c r="Q16" s="27"/>
-      <c r="R16" s="27"/>
-      <c r="S16" s="27"/>
-      <c r="T16" s="27"/>
-      <c r="U16" s="32"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="29"/>
-      <c r="X16" s="29"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="28"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="27"/>
+      <c r="X16" s="27"/>
       <c r="Y16" s="3"/>
     </row>
     <row r="17" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1235,20 +1231,20 @@
       <c r="H17" s="11"/>
       <c r="I17" s="17"/>
       <c r="J17" s="18"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="27"/>
-      <c r="O17" s="27"/>
-      <c r="P17" s="27"/>
-      <c r="Q17" s="27"/>
-      <c r="R17" s="27"/>
-      <c r="S17" s="27"/>
-      <c r="T17" s="27"/>
-      <c r="U17" s="32"/>
-      <c r="V17" s="32"/>
-      <c r="W17" s="29"/>
-      <c r="X17" s="29"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="28"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="30"/>
+      <c r="W17" s="27"/>
+      <c r="X17" s="27"/>
       <c r="Y17" s="3"/>
     </row>
     <row r="18" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1262,20 +1258,20 @@
       <c r="H18" s="11"/>
       <c r="I18" s="17"/>
       <c r="J18" s="18"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="32"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="29"/>
-      <c r="X18" s="29"/>
+      <c r="K18" s="28"/>
+      <c r="L18" s="28"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="27"/>
+      <c r="X18" s="27"/>
       <c r="Y18" s="3"/>
     </row>
     <row r="19" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1289,20 +1285,20 @@
       <c r="H19" s="11"/>
       <c r="I19" s="17"/>
       <c r="J19" s="18"/>
-      <c r="K19" s="31"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-      <c r="P19" s="27"/>
-      <c r="Q19" s="27"/>
-      <c r="R19" s="27"/>
-      <c r="S19" s="27"/>
-      <c r="T19" s="27"/>
-      <c r="U19" s="32"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="29"/>
-      <c r="X19" s="29"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="28"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="27"/>
+      <c r="X19" s="27"/>
       <c r="Y19" s="3"/>
     </row>
     <row r="20" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1316,20 +1312,20 @@
       <c r="H20" s="11"/>
       <c r="I20" s="17"/>
       <c r="J20" s="18"/>
-      <c r="K20" s="31"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="27"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="27"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="32"/>
-      <c r="V20" s="32"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="28"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="27"/>
+      <c r="X20" s="27"/>
       <c r="Y20" s="3"/>
     </row>
     <row r="21" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1343,20 +1339,20 @@
       <c r="H21" s="11"/>
       <c r="I21" s="17"/>
       <c r="J21" s="18"/>
-      <c r="K21" s="31"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="32"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="29"/>
-      <c r="X21" s="29"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="28"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="27"/>
+      <c r="X21" s="27"/>
       <c r="Y21" s="3"/>
     </row>
     <row r="22" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1370,20 +1366,20 @@
       <c r="H22" s="11"/>
       <c r="I22" s="17"/>
       <c r="J22" s="18"/>
-      <c r="K22" s="31"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="32"/>
-      <c r="V22" s="32"/>
-      <c r="W22" s="29"/>
-      <c r="X22" s="29"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="30"/>
+      <c r="W22" s="27"/>
+      <c r="X22" s="27"/>
       <c r="Y22" s="3"/>
     </row>
     <row r="23" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1397,20 +1393,20 @@
       <c r="H23" s="11"/>
       <c r="I23" s="17"/>
       <c r="J23" s="18"/>
-      <c r="K23" s="31"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="32"/>
-      <c r="V23" s="32"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="28"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="27"/>
+      <c r="X23" s="27"/>
       <c r="Y23" s="3"/>
     </row>
     <row r="24" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1424,20 +1420,20 @@
       <c r="H24" s="11"/>
       <c r="I24" s="17"/>
       <c r="J24" s="18"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="32"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="29"/>
-      <c r="X24" s="29"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="28"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="27"/>
+      <c r="X24" s="27"/>
       <c r="Y24" s="3"/>
     </row>
     <row r="25" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1451,20 +1447,20 @@
       <c r="H25" s="11"/>
       <c r="I25" s="17"/>
       <c r="J25" s="18"/>
-      <c r="K25" s="31"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="32"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="29"/>
-      <c r="X25" s="29"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="27"/>
+      <c r="X25" s="27"/>
       <c r="Y25" s="3"/>
     </row>
     <row r="26" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1478,20 +1474,20 @@
       <c r="H26" s="11"/>
       <c r="I26" s="17"/>
       <c r="J26" s="18"/>
-      <c r="K26" s="31"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="32"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
+      <c r="K26" s="28"/>
+      <c r="L26" s="28"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="27"/>
+      <c r="X26" s="27"/>
       <c r="Y26" s="3"/>
     </row>
     <row r="27" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1505,20 +1501,20 @@
       <c r="H27" s="11"/>
       <c r="I27" s="17"/>
       <c r="J27" s="18"/>
-      <c r="K27" s="31"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="32"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="29"/>
-      <c r="X27" s="29"/>
+      <c r="K27" s="28"/>
+      <c r="L27" s="28"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="30"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="27"/>
+      <c r="X27" s="27"/>
       <c r="Y27" s="3"/>
     </row>
     <row r="28" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1532,20 +1528,20 @@
       <c r="H28" s="11"/>
       <c r="I28" s="17"/>
       <c r="J28" s="18"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="28"/>
-      <c r="V28" s="28"/>
-      <c r="W28" s="29"/>
-      <c r="X28" s="29"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="26"/>
+      <c r="V28" s="26"/>
+      <c r="W28" s="27"/>
+      <c r="X28" s="27"/>
     </row>
     <row r="29" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12"/>
@@ -1558,20 +1554,20 @@
       <c r="H29" s="11"/>
       <c r="I29" s="17"/>
       <c r="J29" s="18"/>
-      <c r="K29" s="31"/>
-      <c r="L29" s="31"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="32"/>
-      <c r="V29" s="32"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="27"/>
+      <c r="X29" s="27"/>
       <c r="Y29" s="3"/>
     </row>
     <row r="30" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1585,20 +1581,20 @@
       <c r="H30" s="11"/>
       <c r="I30" s="18"/>
       <c r="J30" s="18"/>
-      <c r="K30" s="31"/>
-      <c r="L30" s="31"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="28"/>
-      <c r="V30" s="28"/>
-      <c r="W30" s="29"/>
-      <c r="X30" s="29"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="25"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="25"/>
+      <c r="P30" s="25"/>
+      <c r="Q30" s="25"/>
+      <c r="R30" s="25"/>
+      <c r="S30" s="25"/>
+      <c r="T30" s="25"/>
+      <c r="U30" s="26"/>
+      <c r="V30" s="26"/>
+      <c r="W30" s="27"/>
+      <c r="X30" s="27"/>
     </row>
     <row r="31" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12"/>
@@ -1611,20 +1607,20 @@
       <c r="H31" s="11"/>
       <c r="I31" s="18"/>
       <c r="J31" s="18"/>
-      <c r="K31" s="31"/>
-      <c r="L31" s="31"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="28"/>
-      <c r="V31" s="28"/>
-      <c r="W31" s="29"/>
-      <c r="X31" s="29"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="25"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="25"/>
+      <c r="P31" s="25"/>
+      <c r="Q31" s="25"/>
+      <c r="R31" s="25"/>
+      <c r="S31" s="25"/>
+      <c r="T31" s="25"/>
+      <c r="U31" s="26"/>
+      <c r="V31" s="26"/>
+      <c r="W31" s="27"/>
+      <c r="X31" s="27"/>
     </row>
     <row r="32" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12"/>
@@ -1637,20 +1633,20 @@
       <c r="H32" s="11"/>
       <c r="I32" s="18"/>
       <c r="J32" s="18"/>
-      <c r="K32" s="31"/>
-      <c r="L32" s="31"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="32"/>
-      <c r="V32" s="32"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="25"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="25"/>
+      <c r="P32" s="25"/>
+      <c r="Q32" s="25"/>
+      <c r="R32" s="25"/>
+      <c r="S32" s="25"/>
+      <c r="T32" s="25"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="27"/>
+      <c r="X32" s="27"/>
       <c r="Y32" s="3"/>
     </row>
     <row r="33" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1664,20 +1660,20 @@
       <c r="H33" s="11"/>
       <c r="I33" s="18"/>
       <c r="J33" s="18"/>
-      <c r="K33" s="31"/>
-      <c r="L33" s="31"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="28"/>
-      <c r="V33" s="28"/>
-      <c r="W33" s="29"/>
-      <c r="X33" s="29"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="26"/>
+      <c r="V33" s="26"/>
+      <c r="W33" s="27"/>
+      <c r="X33" s="27"/>
     </row>
     <row r="34" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12"/>
@@ -1690,20 +1686,20 @@
       <c r="H34" s="11"/>
       <c r="I34" s="18"/>
       <c r="J34" s="18"/>
-      <c r="K34" s="31"/>
-      <c r="L34" s="31"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="28"/>
-      <c r="V34" s="28"/>
-      <c r="W34" s="29"/>
-      <c r="X34" s="29"/>
+      <c r="K34" s="28"/>
+      <c r="L34" s="28"/>
+      <c r="M34" s="25"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="25"/>
+      <c r="P34" s="25"/>
+      <c r="Q34" s="25"/>
+      <c r="R34" s="25"/>
+      <c r="S34" s="25"/>
+      <c r="T34" s="25"/>
+      <c r="U34" s="26"/>
+      <c r="V34" s="26"/>
+      <c r="W34" s="27"/>
+      <c r="X34" s="27"/>
     </row>
     <row r="35" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="12"/>
@@ -1716,20 +1712,20 @@
       <c r="H35" s="11"/>
       <c r="I35" s="18"/>
       <c r="J35" s="18"/>
-      <c r="K35" s="31"/>
-      <c r="L35" s="31"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="32"/>
-      <c r="V35" s="32"/>
-      <c r="W35" s="29"/>
-      <c r="X35" s="29"/>
+      <c r="K35" s="28"/>
+      <c r="L35" s="28"/>
+      <c r="M35" s="25"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="25"/>
+      <c r="P35" s="25"/>
+      <c r="Q35" s="25"/>
+      <c r="R35" s="25"/>
+      <c r="S35" s="25"/>
+      <c r="T35" s="25"/>
+      <c r="U35" s="30"/>
+      <c r="V35" s="30"/>
+      <c r="W35" s="27"/>
+      <c r="X35" s="27"/>
       <c r="Y35" s="3"/>
     </row>
     <row r="36" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
@@ -1743,20 +1739,20 @@
       <c r="H36" s="11"/>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
-      <c r="K36" s="31"/>
-      <c r="L36" s="31"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="28"/>
-      <c r="V36" s="28"/>
-      <c r="W36" s="29"/>
-      <c r="X36" s="29"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="25"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="25"/>
+      <c r="P36" s="25"/>
+      <c r="Q36" s="25"/>
+      <c r="R36" s="25"/>
+      <c r="S36" s="25"/>
+      <c r="T36" s="25"/>
+      <c r="U36" s="26"/>
+      <c r="V36" s="26"/>
+      <c r="W36" s="27"/>
+      <c r="X36" s="27"/>
     </row>
     <row r="37" spans="1:25" ht="51" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="3"/>
@@ -1782,6 +1778,196 @@
     </row>
   </sheetData>
   <mergeCells count="214">
+    <mergeCell ref="S33:T33"/>
+    <mergeCell ref="U33:V33"/>
+    <mergeCell ref="W33:X33"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="K33:L33"/>
+    <mergeCell ref="M33:N33"/>
+    <mergeCell ref="O33:P33"/>
+    <mergeCell ref="Q33:R33"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="U31:V31"/>
+    <mergeCell ref="W31:X31"/>
+    <mergeCell ref="K32:L32"/>
+    <mergeCell ref="M32:N32"/>
+    <mergeCell ref="O32:P32"/>
+    <mergeCell ref="Q32:R32"/>
+    <mergeCell ref="S32:T32"/>
+    <mergeCell ref="U32:V32"/>
+    <mergeCell ref="W32:X32"/>
+    <mergeCell ref="K31:L31"/>
+    <mergeCell ref="M31:N31"/>
+    <mergeCell ref="O31:P31"/>
+    <mergeCell ref="Q31:R31"/>
+    <mergeCell ref="U29:V29"/>
+    <mergeCell ref="W29:X29"/>
+    <mergeCell ref="K30:L30"/>
+    <mergeCell ref="M30:N30"/>
+    <mergeCell ref="O30:P30"/>
+    <mergeCell ref="Q30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="U30:V30"/>
+    <mergeCell ref="W30:X30"/>
+    <mergeCell ref="S14:T14"/>
+    <mergeCell ref="U14:V14"/>
+    <mergeCell ref="W14:X14"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="O28:P28"/>
+    <mergeCell ref="Q28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="U28:V28"/>
+    <mergeCell ref="W28:X28"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="U25:V25"/>
+    <mergeCell ref="W25:X25"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="S12:T12"/>
+    <mergeCell ref="U12:V12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="K26:L26"/>
+    <mergeCell ref="M26:N26"/>
+    <mergeCell ref="O26:P26"/>
+    <mergeCell ref="Q26:R26"/>
+    <mergeCell ref="S26:T26"/>
+    <mergeCell ref="U26:V26"/>
+    <mergeCell ref="S21:T21"/>
+    <mergeCell ref="U21:V21"/>
+    <mergeCell ref="S19:T19"/>
+    <mergeCell ref="U19:V19"/>
+    <mergeCell ref="S17:T17"/>
+    <mergeCell ref="U17:V17"/>
+    <mergeCell ref="S15:T15"/>
+    <mergeCell ref="U15:V15"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="W26:X26"/>
+    <mergeCell ref="K25:L25"/>
+    <mergeCell ref="M25:N25"/>
+    <mergeCell ref="O25:P25"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="S23:T23"/>
+    <mergeCell ref="U23:V23"/>
+    <mergeCell ref="W23:X23"/>
+    <mergeCell ref="K24:L24"/>
+    <mergeCell ref="M24:N24"/>
+    <mergeCell ref="O24:P24"/>
+    <mergeCell ref="Q24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="U24:V24"/>
+    <mergeCell ref="W24:X24"/>
+    <mergeCell ref="K23:L23"/>
+    <mergeCell ref="M23:N23"/>
+    <mergeCell ref="O23:P23"/>
+    <mergeCell ref="Q23:R23"/>
+    <mergeCell ref="W21:X21"/>
+    <mergeCell ref="K22:L22"/>
+    <mergeCell ref="M22:N22"/>
+    <mergeCell ref="O22:P22"/>
+    <mergeCell ref="Q22:R22"/>
+    <mergeCell ref="S22:T22"/>
+    <mergeCell ref="U22:V22"/>
+    <mergeCell ref="W22:X22"/>
+    <mergeCell ref="K21:L21"/>
+    <mergeCell ref="M21:N21"/>
+    <mergeCell ref="O21:P21"/>
+    <mergeCell ref="Q21:R21"/>
+    <mergeCell ref="W19:X19"/>
+    <mergeCell ref="K20:L20"/>
+    <mergeCell ref="M20:N20"/>
+    <mergeCell ref="O20:P20"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="S20:T20"/>
+    <mergeCell ref="U20:V20"/>
+    <mergeCell ref="W20:X20"/>
+    <mergeCell ref="K19:L19"/>
+    <mergeCell ref="M19:N19"/>
+    <mergeCell ref="O19:P19"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="W17:X17"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="S18:T18"/>
+    <mergeCell ref="U18:V18"/>
+    <mergeCell ref="W18:X18"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="O17:P17"/>
+    <mergeCell ref="Q17:R17"/>
+    <mergeCell ref="S13:T13"/>
+    <mergeCell ref="U13:V13"/>
+    <mergeCell ref="W13:X13"/>
+    <mergeCell ref="M29:N29"/>
+    <mergeCell ref="O29:P29"/>
+    <mergeCell ref="Q29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="K27:L27"/>
+    <mergeCell ref="M27:N27"/>
+    <mergeCell ref="O27:P27"/>
+    <mergeCell ref="Q27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="W15:X15"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="O16:P16"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="S16:T16"/>
+    <mergeCell ref="U16:V16"/>
+    <mergeCell ref="W16:X16"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="O15:P15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="H7:H11"/>
+    <mergeCell ref="I7:I11"/>
+    <mergeCell ref="J7:J11"/>
+    <mergeCell ref="K7:L11"/>
+    <mergeCell ref="W7:W11"/>
+    <mergeCell ref="C7:C11"/>
+    <mergeCell ref="D7:D11"/>
+    <mergeCell ref="M7:N11"/>
+    <mergeCell ref="O7:P11"/>
+    <mergeCell ref="Q7:R11"/>
+    <mergeCell ref="U7:V7"/>
+    <mergeCell ref="U9:V9"/>
+    <mergeCell ref="U10:V10"/>
+    <mergeCell ref="U11:V11"/>
+    <mergeCell ref="U8:V8"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="E7:E11"/>
+    <mergeCell ref="K35:L35"/>
+    <mergeCell ref="M35:N35"/>
+    <mergeCell ref="O35:P35"/>
+    <mergeCell ref="Q35:R35"/>
+    <mergeCell ref="S35:T35"/>
+    <mergeCell ref="S7:T11"/>
+    <mergeCell ref="X3:Y3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="C4:K4"/>
+    <mergeCell ref="L4:M4"/>
+    <mergeCell ref="N4:O4"/>
+    <mergeCell ref="P4:Q4"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="V4:W4"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="E3:U3"/>
+    <mergeCell ref="V3:W3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="E5:Y5"/>
+    <mergeCell ref="G7:G11"/>
     <mergeCell ref="S36:T36"/>
     <mergeCell ref="U36:V36"/>
     <mergeCell ref="W35:X35"/>
@@ -1806,196 +1992,6 @@
     <mergeCell ref="U34:V34"/>
     <mergeCell ref="W34:X34"/>
     <mergeCell ref="K29:L29"/>
-    <mergeCell ref="A7:A11"/>
-    <mergeCell ref="E7:E11"/>
-    <mergeCell ref="K35:L35"/>
-    <mergeCell ref="M35:N35"/>
-    <mergeCell ref="O35:P35"/>
-    <mergeCell ref="Q35:R35"/>
-    <mergeCell ref="S35:T35"/>
-    <mergeCell ref="S7:T11"/>
-    <mergeCell ref="X3:Y3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="C4:K4"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:Q4"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="T4:U4"/>
-    <mergeCell ref="V4:W4"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:U3"/>
-    <mergeCell ref="V3:W3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:Y5"/>
-    <mergeCell ref="G7:G11"/>
-    <mergeCell ref="H7:H11"/>
-    <mergeCell ref="I7:I11"/>
-    <mergeCell ref="J7:J11"/>
-    <mergeCell ref="K7:L11"/>
-    <mergeCell ref="W7:W11"/>
-    <mergeCell ref="C7:C11"/>
-    <mergeCell ref="D7:D11"/>
-    <mergeCell ref="M7:N11"/>
-    <mergeCell ref="O7:P11"/>
-    <mergeCell ref="Q7:R11"/>
-    <mergeCell ref="U7:V7"/>
-    <mergeCell ref="U9:V9"/>
-    <mergeCell ref="U10:V10"/>
-    <mergeCell ref="U11:V11"/>
-    <mergeCell ref="U8:V8"/>
-    <mergeCell ref="S13:T13"/>
-    <mergeCell ref="U13:V13"/>
-    <mergeCell ref="W13:X13"/>
-    <mergeCell ref="M29:N29"/>
-    <mergeCell ref="O29:P29"/>
-    <mergeCell ref="Q29:R29"/>
-    <mergeCell ref="S29:T29"/>
-    <mergeCell ref="K27:L27"/>
-    <mergeCell ref="M27:N27"/>
-    <mergeCell ref="O27:P27"/>
-    <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="W15:X15"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="O16:P16"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="S16:T16"/>
-    <mergeCell ref="U16:V16"/>
-    <mergeCell ref="W16:X16"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="O15:P15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="W17:X17"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:P18"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="S18:T18"/>
-    <mergeCell ref="U18:V18"/>
-    <mergeCell ref="W18:X18"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="O17:P17"/>
-    <mergeCell ref="Q17:R17"/>
-    <mergeCell ref="W19:X19"/>
-    <mergeCell ref="K20:L20"/>
-    <mergeCell ref="M20:N20"/>
-    <mergeCell ref="O20:P20"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="S20:T20"/>
-    <mergeCell ref="U20:V20"/>
-    <mergeCell ref="W20:X20"/>
-    <mergeCell ref="K19:L19"/>
-    <mergeCell ref="M19:N19"/>
-    <mergeCell ref="O19:P19"/>
-    <mergeCell ref="Q19:R19"/>
-    <mergeCell ref="W21:X21"/>
-    <mergeCell ref="K22:L22"/>
-    <mergeCell ref="M22:N22"/>
-    <mergeCell ref="O22:P22"/>
-    <mergeCell ref="Q22:R22"/>
-    <mergeCell ref="S22:T22"/>
-    <mergeCell ref="U22:V22"/>
-    <mergeCell ref="W22:X22"/>
-    <mergeCell ref="K21:L21"/>
-    <mergeCell ref="M21:N21"/>
-    <mergeCell ref="O21:P21"/>
-    <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="W26:X26"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="M25:N25"/>
-    <mergeCell ref="O25:P25"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="S23:T23"/>
-    <mergeCell ref="U23:V23"/>
-    <mergeCell ref="W23:X23"/>
-    <mergeCell ref="K24:L24"/>
-    <mergeCell ref="M24:N24"/>
-    <mergeCell ref="O24:P24"/>
-    <mergeCell ref="Q24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="U24:V24"/>
-    <mergeCell ref="W24:X24"/>
-    <mergeCell ref="K23:L23"/>
-    <mergeCell ref="M23:N23"/>
-    <mergeCell ref="O23:P23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="S12:T12"/>
-    <mergeCell ref="U12:V12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="K26:L26"/>
-    <mergeCell ref="M26:N26"/>
-    <mergeCell ref="O26:P26"/>
-    <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="U26:V26"/>
-    <mergeCell ref="S21:T21"/>
-    <mergeCell ref="U21:V21"/>
-    <mergeCell ref="S19:T19"/>
-    <mergeCell ref="U19:V19"/>
-    <mergeCell ref="S17:T17"/>
-    <mergeCell ref="U17:V17"/>
-    <mergeCell ref="S15:T15"/>
-    <mergeCell ref="U15:V15"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="K30:L30"/>
-    <mergeCell ref="M30:N30"/>
-    <mergeCell ref="O30:P30"/>
-    <mergeCell ref="Q30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="U30:V30"/>
-    <mergeCell ref="W30:X30"/>
-    <mergeCell ref="S14:T14"/>
-    <mergeCell ref="U14:V14"/>
-    <mergeCell ref="W14:X14"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="O28:P28"/>
-    <mergeCell ref="Q28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="U28:V28"/>
-    <mergeCell ref="W28:X28"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="U25:V25"/>
-    <mergeCell ref="W25:X25"/>
-    <mergeCell ref="S33:T33"/>
-    <mergeCell ref="U33:V33"/>
-    <mergeCell ref="W33:X33"/>
-    <mergeCell ref="B7:B11"/>
-    <mergeCell ref="K33:L33"/>
-    <mergeCell ref="M33:N33"/>
-    <mergeCell ref="O33:P33"/>
-    <mergeCell ref="Q33:R33"/>
-    <mergeCell ref="S31:T31"/>
-    <mergeCell ref="U31:V31"/>
-    <mergeCell ref="W31:X31"/>
-    <mergeCell ref="K32:L32"/>
-    <mergeCell ref="M32:N32"/>
-    <mergeCell ref="O32:P32"/>
-    <mergeCell ref="Q32:R32"/>
-    <mergeCell ref="S32:T32"/>
-    <mergeCell ref="U32:V32"/>
-    <mergeCell ref="W32:X32"/>
-    <mergeCell ref="K31:L31"/>
-    <mergeCell ref="M31:N31"/>
-    <mergeCell ref="O31:P31"/>
-    <mergeCell ref="Q31:R31"/>
-    <mergeCell ref="U29:V29"/>
-    <mergeCell ref="W29:X29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
